--- a/InputData/add-outputs/VoaSL/Value of a Statistical Life.xlsx
+++ b/InputData/add-outputs/VoaSL/Value of a Statistical Life.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\World Resources Institute\TRAC City - HK 2050 is now\eps-1.4.3-hk-wipB\eps-1.4.3-hk-wipB\InputData\add-outputs\VoaSL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://civicexchangeorg.sharepoint.com/sites/HongKong2050isNowTeamsite/Shared Documents/12 Hong Kong EPS technical note/HK EPS update/eps-us-3.4.7 working/InputData/add-outputs/VoaSL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AB7C9A337BB36FE76E84E66B932EE341CB00D162" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{4FB19959-348F-407C-A9FD-793088147DC4}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{0E59E064-EF61-4312-82D8-C31F8060157D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7242887C-A4DD-554E-806D-1C630E751419}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12140" yWindow="500" windowWidth="17300" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="VoaSL" sheetId="3" r:id="rId3"/>
+    <sheet name="VoaSL" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>VoaSL Value of a Statistical Life</t>
   </si>
@@ -38,6 +39,51 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>U.S. Environmental Protection Agency</t>
+  </si>
+  <si>
+    <t>Frequently Asked Questions on Mortality Risk Valuation</t>
+  </si>
+  <si>
+    <t>We adjust 2006 dollars to 2012 dollars using the following conversion factor:</t>
+  </si>
+  <si>
+    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>"What value of statistical life does EPA use?"</t>
+  </si>
+  <si>
+    <t>Statistical Life</t>
+  </si>
+  <si>
+    <t>This variable is used to convert from dollars (in the SCoHIbP Social Cost of</t>
+  </si>
+  <si>
+    <t>Health Impacts by Pollutant variable) into human lives, so the VSL figure</t>
+  </si>
+  <si>
+    <t>here must reflect the one used to calculate the health impacts in that</t>
+  </si>
+  <si>
+    <t>variable for the result to be accurate.</t>
+  </si>
+  <si>
+    <t>Currency Year Adjustment</t>
+  </si>
+  <si>
+    <t>2012$/life</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>https://www.epa.gov/environmental-economics/mortality-risk-valuation#whatvalue</t>
+  </si>
+  <si>
     <t>Hua Wang and Jie He, World Bank Development Research Group</t>
   </si>
   <si>
@@ -50,21 +96,6 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable is used to convert from dollars (in the SCoHIbP Social Cost of</t>
-  </si>
-  <si>
-    <t>Health Impacts by Pollutant variable) into human lives, so the VSL figure</t>
-  </si>
-  <si>
-    <t>here must reflect the one used to calculate the health impacts in that</t>
-  </si>
-  <si>
-    <t>variable for the result to be accurate.</t>
-  </si>
-  <si>
     <t>China VoaSL data</t>
   </si>
   <si>
@@ -75,12 +106,6 @@
   </si>
   <si>
     <t>USD</t>
-  </si>
-  <si>
-    <t>Statistical Life</t>
-  </si>
-  <si>
-    <t>Value (2012$)</t>
   </si>
 </sst>
 </file>
@@ -112,15 +137,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -128,23 +159,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -164,9 +241,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,9 +281,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -239,26 +316,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -291,26 +351,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,154 +527,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="38.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="F3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="3">
+        <v>2013</v>
+      </c>
+      <c r="F4" s="8">
         <v>2010</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{C8A0D264-030B-4C66-9744-137C1B55BFB9}"/>
+    <hyperlink ref="B6" r:id="rId1" location="whatvalue" display="https://www.epa.gov/environmental-economics/mortality-risk-valuation - whatvalue" xr:uid="{F4EA8DF9-36E3-4A47-8B4C-6E99399B200A}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{2A9A3D53-DEEE-9F4D-A5BD-A3E5CFEC8421}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>795000</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0.14573</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <f>A3*A5</f>
-        <v>115855.35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="1" max="2" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6">
-        <f>Data!A7</f>
+      <c r="B2" s="13">
+        <f>A10</f>
         <v>115855.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>795000</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>0.14573</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
+        <f>A6*A8</f>
+        <v>115855.35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -640,31 +729,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -672,24 +762,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -708,70 +859,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -885,18 +989,35 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb176f07-3112-4ee9-93fd-ae2cb5f3e433">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b15a3a4-8173-42d6-9deb-398ec38eca4b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7781F9-6353-4A61-823B-CE6E96243302}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D24395-346C-4C33-A7ED-2569E64DEB7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7ABCA70-D359-45C2-BB14-0B78385CACBF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53D1E6C-45E5-4B0E-9E0D-4AA345292372}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -904,19 +1025,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C035858-B5F2-4371-B64A-296D500AB545}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A171F1-88D9-4178-B0F7-1471973D2987}"/>
 </file>